--- a/Book 6.xlsx
+++ b/Book 6.xlsx
@@ -1,37 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{736C4220-2887-4AE1-971A-BAB23630900D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29910"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Vishu\Documents\UiPath\PrestaShopAutomation\FridayPPT_PrestaShop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <si>
     <t>FirstName</t>
   </si>
@@ -39,13 +26,67 @@
     <t>LastName</t>
   </si>
   <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>ProductName</t>
+  </si>
+  <si>
+    <t>customMessage</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Zip</t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>ShippingComment</t>
+  </si>
+  <si>
+    <t>Language</t>
+  </si>
+  <si>
     <t>DOB</t>
   </si>
   <si>
-    <t>Product1</t>
-  </si>
-  <si>
-    <t>Gender</t>
+    <t>NewDOB</t>
+  </si>
+  <si>
+    <t>NewPassword</t>
+  </si>
+  <si>
+    <t>NewAddress</t>
+  </si>
+  <si>
+    <t>NewCity</t>
+  </si>
+  <si>
+    <t>NewZip</t>
+  </si>
+  <si>
+    <t>NewState</t>
+  </si>
+  <si>
+    <t>SubscribeMail</t>
+  </si>
+  <si>
+    <t>MessageBox</t>
+  </si>
+  <si>
+    <t>BrowserOption</t>
   </si>
   <si>
     <t>Test</t>
@@ -54,23 +95,348 @@
     <t>User</t>
   </si>
   <si>
-    <t>T shirt</t>
+    <t>abc267@gmail.com</t>
+  </si>
+  <si>
+    <t>Mugs</t>
   </si>
   <si>
     <t>Male</t>
+  </si>
+  <si>
+    <t>Customizable mug</t>
+  </si>
+  <si>
+    <t>Happy Birthday</t>
+  </si>
+  <si>
+    <t>221 Baker Street</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Please send items asap</t>
+  </si>
+  <si>
+    <t>Galego</t>
+  </si>
+  <si>
+    <t>02/12/2000</t>
+  </si>
+  <si>
+    <t>03/19/2001</t>
+  </si>
+  <si>
+    <t>ssousgaoQ@35698395</t>
+  </si>
+  <si>
+    <t>225 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity1</t>
+  </si>
+  <si>
+    <t>Alaska</t>
+  </si>
+  <si>
+    <t>test061@gmail.com</t>
+  </si>
+  <si>
+    <t>I recently received my order, but the product delivered is different from what I ordered. The item does not match the product shown on the website.</t>
+  </si>
+  <si>
+    <t>msedge.exe</t>
+  </si>
+  <si>
+    <t>Testing</t>
+  </si>
+  <si>
+    <t>Userr</t>
+  </si>
+  <si>
+    <t>abc278@gmail.com</t>
+  </si>
+  <si>
+    <t>Mug The adventure begins</t>
+  </si>
+  <si>
+    <t>Happy Anniversary</t>
+  </si>
+  <si>
+    <t>222 Baker Street</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>Please send items at give address only</t>
+  </si>
+  <si>
+    <t>English</t>
+  </si>
+  <si>
+    <t>02/12/2001</t>
+  </si>
+  <si>
+    <t>03/19/2002</t>
+  </si>
+  <si>
+    <t>226 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity2</t>
+  </si>
+  <si>
+    <t>testing002@gmail.com</t>
+  </si>
+  <si>
+    <t>chrome.exe</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Useer</t>
+  </si>
+  <si>
+    <t>ober052@gmail.com</t>
+  </si>
+  <si>
+    <t>T-shirt</t>
+  </si>
+  <si>
+    <t>Hummingbird printed t-shirt</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>223 Baker Street</t>
+  </si>
+  <si>
+    <t>02/12/2002</t>
+  </si>
+  <si>
+    <t>03/19/2003</t>
+  </si>
+  <si>
+    <t>227 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity3</t>
+  </si>
+  <si>
+    <t>john012@gmail.com</t>
+  </si>
+  <si>
+    <t>Ankit</t>
+  </si>
+  <si>
+    <t>nbr052@gmail.com</t>
+  </si>
+  <si>
+    <t>Frame</t>
+  </si>
+  <si>
+    <t>Pack Mug + Framed poster</t>
+  </si>
+  <si>
+    <t>224 Baker Street</t>
+  </si>
+  <si>
+    <t>02/12/2003</t>
+  </si>
+  <si>
+    <t>03/19/2004</t>
+  </si>
+  <si>
+    <t>228 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity4</t>
+  </si>
+  <si>
+    <t>ankit0142@gmail.com</t>
+  </si>
+  <si>
+    <t>Aman</t>
+  </si>
+  <si>
+    <t>mbr052@gmail.com</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>Mug Today is a good day</t>
+  </si>
+  <si>
+    <t>02/12/2004</t>
+  </si>
+  <si>
+    <t>03/19/2005</t>
+  </si>
+  <si>
+    <t>229 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity5</t>
+  </si>
+  <si>
+    <t>aman042@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayush</t>
+  </si>
+  <si>
+    <t>yb759@gmail.com</t>
+  </si>
+  <si>
+    <t>02/12/2005</t>
+  </si>
+  <si>
+    <t>03/19/2006</t>
+  </si>
+  <si>
+    <t>230 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity6</t>
+  </si>
+  <si>
+    <t>ayush082@gmail.com</t>
+  </si>
+  <si>
+    <t>Sahil</t>
+  </si>
+  <si>
+    <t>ay282@gmail.com</t>
+  </si>
+  <si>
+    <t>02/12/2006</t>
+  </si>
+  <si>
+    <t>03/19/2007</t>
+  </si>
+  <si>
+    <t>231 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity7</t>
+  </si>
+  <si>
+    <t>sahil082@gmail.com</t>
+  </si>
+  <si>
+    <t>Amar</t>
+  </si>
+  <si>
+    <t>02/12/2007</t>
+  </si>
+  <si>
+    <t>03/19/2008</t>
+  </si>
+  <si>
+    <t>232 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity8</t>
+  </si>
+  <si>
+    <t>amar002@gmail.com</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>mbr022@gmail.com</t>
+  </si>
+  <si>
+    <t>02/12/2008</t>
+  </si>
+  <si>
+    <t>03/19/2009</t>
+  </si>
+  <si>
+    <t>233 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity9</t>
+  </si>
+  <si>
+    <t>amit072@gmail.com</t>
+  </si>
+  <si>
+    <t>Manpreet</t>
+  </si>
+  <si>
+    <t>asb023@gmail.com</t>
+  </si>
+  <si>
+    <t>02/12/2009</t>
+  </si>
+  <si>
+    <t>03/19/2010</t>
+  </si>
+  <si>
+    <t>234 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity10</t>
+  </si>
+  <si>
+    <t>manpreet703@gmail.com</t>
+  </si>
+  <si>
+    <t>Naman</t>
+  </si>
+  <si>
+    <t>abr023@gmail.com</t>
+  </si>
+  <si>
+    <t>02/12/2010</t>
+  </si>
+  <si>
+    <t>03/19/2011</t>
+  </si>
+  <si>
+    <t>235 Baker Street</t>
+  </si>
+  <si>
+    <t>TestCity11</t>
+  </si>
+  <si>
+    <t>naman373@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -82,34 +448,28 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -118,10 +478,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -290,6 +650,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -316,24 +677,25 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -394,31 +756,38 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E2"/>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.855469" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.710938" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21" customWidth="1"/>
+    <col min="6" max="6" width="32" customWidth="1"/>
+    <col min="7" max="7" width="17.28516" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.57031" customWidth="1"/>
+    <col min="9" max="9" width="10.71094" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578" customWidth="1"/>
+    <col min="11" max="11" width="11.71094" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="34.14063" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.14063" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="20.85547" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.42578" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.285156" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="22.71094" customWidth="1"/>
+    <col min="22" max="22" width="36.57031" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.14063" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -434,25 +803,755 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>25933</v>
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="1">
+        <v>70081</v>
+      </c>
+      <c r="K2" t="s">
+        <v>31</v>
+      </c>
+      <c r="L2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M2" t="s">
+        <v>33</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="P2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>37</v>
+      </c>
+      <c r="R2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S2">
+        <v>12341</v>
+      </c>
+      <c r="T2" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
+        <v>48</v>
+      </c>
+      <c r="I3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="1">
+        <v>70091</v>
+      </c>
+      <c r="K3" t="s">
+        <v>50</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>55</v>
+      </c>
+      <c r="R3" t="s">
+        <v>56</v>
+      </c>
+      <c r="S3">
+        <v>12342</v>
+      </c>
+      <c r="T3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W3" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>63</v>
+      </c>
+      <c r="G4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" t="s">
+        <v>65</v>
+      </c>
+      <c r="I4" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="1">
+        <v>70092</v>
+      </c>
+      <c r="K4" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="P4" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>68</v>
+      </c>
+      <c r="R4" t="s">
+        <v>69</v>
+      </c>
+      <c r="S4">
+        <v>12343</v>
+      </c>
+      <c r="T4" t="s">
+        <v>39</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" t="s">
+        <v>64</v>
+      </c>
+      <c r="H5" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J5" s="1">
+        <v>70093</v>
+      </c>
+      <c r="K5" t="s">
+        <v>50</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>78</v>
+      </c>
+      <c r="R5" t="s">
+        <v>79</v>
+      </c>
+      <c r="S5">
+        <v>12344</v>
+      </c>
+      <c r="T5" t="s">
+        <v>39</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" t="s">
+        <v>83</v>
+      </c>
+      <c r="F6" t="s">
+        <v>84</v>
+      </c>
+      <c r="G6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" t="s">
+        <v>49</v>
+      </c>
+      <c r="J6" s="1">
+        <v>70094</v>
+      </c>
+      <c r="K6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="P6" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>87</v>
+      </c>
+      <c r="R6" t="s">
+        <v>88</v>
+      </c>
+      <c r="S6">
+        <v>12345</v>
+      </c>
+      <c r="T6" t="s">
+        <v>39</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" t="s">
+        <v>49</v>
+      </c>
+      <c r="J7" s="1">
+        <v>70095</v>
+      </c>
+      <c r="K7" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="P7" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>94</v>
+      </c>
+      <c r="R7" t="s">
+        <v>95</v>
+      </c>
+      <c r="S7">
+        <v>12346</v>
+      </c>
+      <c r="T7" t="s">
+        <v>39</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I8" t="s">
+        <v>49</v>
+      </c>
+      <c r="J8" s="1">
+        <v>70096</v>
+      </c>
+      <c r="K8" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="P8" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>101</v>
+      </c>
+      <c r="R8" t="s">
+        <v>102</v>
+      </c>
+      <c r="S8">
+        <v>12347</v>
+      </c>
+      <c r="T8" t="s">
+        <v>39</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J9" s="1">
+        <v>70097</v>
+      </c>
+      <c r="K9" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="P9" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>107</v>
+      </c>
+      <c r="R9" t="s">
+        <v>108</v>
+      </c>
+      <c r="S9">
+        <v>12348</v>
+      </c>
+      <c r="T9" t="s">
+        <v>39</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H10" t="s">
+        <v>87</v>
+      </c>
+      <c r="I10" t="s">
+        <v>49</v>
+      </c>
+      <c r="J10" s="1">
+        <v>70098</v>
+      </c>
+      <c r="K10" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="P10" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>114</v>
+      </c>
+      <c r="R10" t="s">
+        <v>115</v>
+      </c>
+      <c r="S10">
+        <v>12349</v>
+      </c>
+      <c r="T10" t="s">
+        <v>39</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E11" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" t="s">
+        <v>49</v>
+      </c>
+      <c r="J11" s="1">
+        <v>70099</v>
+      </c>
+      <c r="K11" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="P11" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>121</v>
+      </c>
+      <c r="R11" t="s">
+        <v>122</v>
+      </c>
+      <c r="S11">
+        <v>12350</v>
+      </c>
+      <c r="T11" t="s">
+        <v>39</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>124</v>
+      </c>
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" t="s">
+        <v>49</v>
+      </c>
+      <c r="J12" s="1">
+        <v>70100</v>
+      </c>
+      <c r="K12" t="s">
+        <v>50</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="P12" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>128</v>
+      </c>
+      <c r="R12" t="s">
+        <v>129</v>
+      </c>
+      <c r="S12">
+        <v>12351</v>
+      </c>
+      <c r="T12" t="s">
+        <v>39</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" s="2"/>
+    </row>
+    <row r="14">
+      <c r="C14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="C15" s="2"/>
+    </row>
+    <row r="16">
+      <c r="C16" s="2"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="2"/>
+    </row>
+    <row r="18">
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20">
+      <c r="C20" s="2"/>
+    </row>
+    <row r="21">
+      <c r="C21" s="2"/>
+    </row>
+    <row r="22">
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23">
+      <c r="C23" s="2"/>
+    </row>
+    <row r="24">
+      <c r="C24" s="2"/>
+    </row>
+    <row r="25">
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26">
+      <c r="C26" s="2"/>
+    </row>
+    <row r="27">
+      <c r="C27" s="2"/>
+    </row>
+    <row r="28">
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29">
+      <c r="C29" s="2"/>
+    </row>
+    <row r="30">
+      <c r="C30" s="2"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <hyperlinks>
+    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="C2" r:id="rId2"/>
+    <hyperlink ref="C3" r:id="rId3"/>
+    <hyperlink ref="U3" r:id="rId4"/>
+    <hyperlink ref="U4" r:id="rId5"/>
+    <hyperlink ref="U5" r:id="rId6"/>
+    <hyperlink ref="U6" r:id="rId7"/>
+    <hyperlink ref="U7" r:id="rId8"/>
+    <hyperlink ref="U8" r:id="rId9"/>
+    <hyperlink ref="U9" r:id="rId10"/>
+    <hyperlink ref="U10" r:id="rId11"/>
+    <hyperlink ref="U11" r:id="rId12"/>
+    <hyperlink ref="C10" r:id="rId13"/>
+    <hyperlink ref="C9" r:id="rId14"/>
+    <hyperlink ref="C8" r:id="rId15"/>
+    <hyperlink ref="C7" r:id="rId16"/>
+    <hyperlink ref="C6" r:id="rId17"/>
+    <hyperlink ref="C5" r:id="rId18"/>
+    <hyperlink ref="C4" r:id="rId19"/>
+    <hyperlink ref="C11" r:id="rId20"/>
+    <hyperlink ref="C12" r:id="rId21"/>
+    <hyperlink ref="U12" r:id="rId22"/>
+  </hyperlinks>
 </worksheet>
 </file>
--- a/Book 6.xlsx
+++ b/Book 6.xlsx
@@ -47,10 +47,13 @@
     <t>City</t>
   </si>
   <si>
+    <t>States</t>
+  </si>
+  <si>
     <t>Zip</t>
   </si>
   <si>
-    <t>State</t>
+    <t>Country</t>
   </si>
   <si>
     <t>ShippingComment</t>
@@ -95,7 +98,7 @@
     <t>User</t>
   </si>
   <si>
-    <t>abc267@gmail.com</t>
+    <t>abc700@gmail.com</t>
   </si>
   <si>
     <t>Mugs</t>
@@ -116,6 +119,12 @@
     <t>New York</t>
   </si>
   <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
     <t>Please send items asap</t>
   </si>
   <si>
@@ -155,9 +164,6 @@
     <t>Userr</t>
   </si>
   <si>
-    <t>abc278@gmail.com</t>
-  </si>
-  <si>
     <t>Mug The adventure begins</t>
   </si>
   <si>
@@ -170,9 +176,6 @@
     <t>New Jersey</t>
   </si>
   <si>
-    <t>New Mexico</t>
-  </si>
-  <si>
     <t>Please send items at give address only</t>
   </si>
   <si>
@@ -203,7 +206,7 @@
     <t>Useer</t>
   </si>
   <si>
-    <t>ober052@gmail.com</t>
+    <t>abc7001@gmail.com</t>
   </si>
   <si>
     <t>T-shirt</t>
@@ -236,7 +239,7 @@
     <t>Ankit</t>
   </si>
   <si>
-    <t>nbr052@gmail.com</t>
+    <t>abc7002@gmail.com</t>
   </si>
   <si>
     <t>Frame</t>
@@ -266,7 +269,7 @@
     <t>Aman</t>
   </si>
   <si>
-    <t>mbr052@gmail.com</t>
+    <t>abc70023@gmail.com</t>
   </si>
   <si>
     <t>Female</t>
@@ -293,7 +296,7 @@
     <t>Ayush</t>
   </si>
   <si>
-    <t>yb759@gmail.com</t>
+    <t>abc7004@gmail.com</t>
   </si>
   <si>
     <t>02/12/2005</t>
@@ -314,7 +317,7 @@
     <t>Sahil</t>
   </si>
   <si>
-    <t>ay282@gmail.com</t>
+    <t>abc7005@gmail.com</t>
   </si>
   <si>
     <t>02/12/2006</t>
@@ -335,6 +338,9 @@
     <t>Amar</t>
   </si>
   <si>
+    <t>abc7006@gmail.com</t>
+  </si>
+  <si>
     <t>02/12/2007</t>
   </si>
   <si>
@@ -353,7 +359,7 @@
     <t>Amit</t>
   </si>
   <si>
-    <t>mbr022@gmail.com</t>
+    <t>abc7007@gmail.com</t>
   </si>
   <si>
     <t>02/12/2008</t>
@@ -374,7 +380,7 @@
     <t>Manpreet</t>
   </si>
   <si>
-    <t>asb023@gmail.com</t>
+    <t>abc7008@gmail.com</t>
   </si>
   <si>
     <t>02/12/2009</t>
@@ -395,7 +401,7 @@
     <t>Naman</t>
   </si>
   <si>
-    <t>abr023@gmail.com</t>
+    <t>abc7009@gmail.com</t>
   </si>
   <si>
     <t>02/12/2010</t>
@@ -775,16 +781,17 @@
     <col min="7" max="7" width="17.28516" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="22.57031" customWidth="1"/>
     <col min="9" max="9" width="10.71094" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578" customWidth="1"/>
-    <col min="11" max="11" width="11.71094" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="34.14063" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.14063" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.85547" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.42578" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.285156" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="22.71094" customWidth="1"/>
-    <col min="22" max="22" width="36.57031" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.14063" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.71094" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578" customWidth="1"/>
+    <col min="12" max="12" width="11.71094" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="34.14063" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="11.14063" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.85547" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.42578" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.285156" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="22.71094" customWidth="1"/>
+    <col min="23" max="23" width="36.57031" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.14063" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -815,10 +822,10 @@
       <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -857,621 +864,657 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>31</v>
-      </c>
-      <c r="J2" s="1">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K2" s="1">
         <v>70081</v>
       </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
       <c r="L2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="N2" t="s">
+        <v>36</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="P2" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>38</v>
       </c>
       <c r="Q2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="R2" t="s">
-        <v>38</v>
-      </c>
-      <c r="S2">
+        <v>40</v>
+      </c>
+      <c r="S2" t="s">
+        <v>41</v>
+      </c>
+      <c r="T2">
         <v>12341</v>
       </c>
-      <c r="T2" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="W2" s="4" t="s">
+      <c r="U2" t="s">
         <v>42</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="X2" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="1">
+        <v>51</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" s="1">
         <v>70091</v>
       </c>
-      <c r="K3" t="s">
-        <v>50</v>
-      </c>
-      <c r="L3" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="L3" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="N3" t="s">
         <v>53</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P3" t="s">
-        <v>36</v>
+      <c r="P3" s="3" t="s">
+        <v>55</v>
       </c>
       <c r="Q3" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="R3" t="s">
         <v>56</v>
       </c>
-      <c r="S3">
+      <c r="S3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T3">
         <v>12342</v>
       </c>
-      <c r="T3" t="s">
-        <v>39</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="W3" s="4" t="s">
+      <c r="U3" t="s">
+        <v>42</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>58</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I4" t="s">
-        <v>49</v>
-      </c>
-      <c r="J4" s="1">
+        <v>51</v>
+      </c>
+      <c r="J4" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="1">
         <v>70092</v>
       </c>
-      <c r="K4" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" s="3" t="s">
-        <v>66</v>
+      <c r="L4" t="s">
+        <v>34</v>
       </c>
       <c r="O4" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="P4" t="s">
-        <v>36</v>
+      <c r="P4" s="3" t="s">
+        <v>68</v>
       </c>
       <c r="Q4" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="R4" t="s">
         <v>69</v>
       </c>
-      <c r="S4">
+      <c r="S4" t="s">
+        <v>70</v>
+      </c>
+      <c r="T4">
         <v>12343</v>
       </c>
-      <c r="T4" t="s">
-        <v>39</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>70</v>
+      <c r="U4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I5" t="s">
-        <v>49</v>
-      </c>
-      <c r="J5" s="1">
+        <v>51</v>
+      </c>
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+      <c r="K5" s="1">
         <v>70093</v>
       </c>
-      <c r="K5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>76</v>
+      <c r="L5" t="s">
+        <v>34</v>
       </c>
       <c r="O5" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="P5" t="s">
-        <v>36</v>
+      <c r="P5" s="3" t="s">
+        <v>78</v>
       </c>
       <c r="Q5" t="s">
-        <v>78</v>
+        <v>39</v>
       </c>
       <c r="R5" t="s">
         <v>79</v>
       </c>
-      <c r="S5">
+      <c r="S5" t="s">
+        <v>80</v>
+      </c>
+      <c r="T5">
         <v>12344</v>
       </c>
-      <c r="T5" t="s">
-        <v>39</v>
-      </c>
-      <c r="U5" s="2" t="s">
-        <v>80</v>
+      <c r="U5" t="s">
+        <v>42</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>49</v>
-      </c>
-      <c r="J6" s="1">
+        <v>51</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" s="1">
         <v>70094</v>
       </c>
-      <c r="K6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>85</v>
+      <c r="L6" t="s">
+        <v>34</v>
       </c>
       <c r="O6" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="P6" t="s">
-        <v>36</v>
+      <c r="P6" s="3" t="s">
+        <v>87</v>
       </c>
       <c r="Q6" t="s">
-        <v>87</v>
+        <v>39</v>
       </c>
       <c r="R6" t="s">
         <v>88</v>
       </c>
-      <c r="S6">
+      <c r="S6" t="s">
+        <v>89</v>
+      </c>
+      <c r="T6">
         <v>12345</v>
       </c>
-      <c r="T6" t="s">
-        <v>39</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>89</v>
+      <c r="U6" t="s">
+        <v>42</v>
+      </c>
+      <c r="V6" s="2" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I7" t="s">
-        <v>49</v>
-      </c>
-      <c r="J7" s="1">
+        <v>51</v>
+      </c>
+      <c r="J7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K7" s="1">
         <v>70095</v>
       </c>
-      <c r="K7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>92</v>
+      <c r="L7" t="s">
+        <v>34</v>
       </c>
       <c r="O7" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="P7" t="s">
-        <v>36</v>
+      <c r="P7" s="3" t="s">
+        <v>94</v>
       </c>
       <c r="Q7" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="R7" t="s">
         <v>95</v>
       </c>
-      <c r="S7">
+      <c r="S7" t="s">
+        <v>96</v>
+      </c>
+      <c r="T7">
         <v>12346</v>
       </c>
-      <c r="T7" t="s">
-        <v>39</v>
-      </c>
-      <c r="U7" s="2" t="s">
-        <v>96</v>
+      <c r="U7" t="s">
+        <v>42</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I8" t="s">
-        <v>49</v>
-      </c>
-      <c r="J8" s="1">
+        <v>51</v>
+      </c>
+      <c r="J8" t="s">
+        <v>33</v>
+      </c>
+      <c r="K8" s="1">
         <v>70096</v>
       </c>
-      <c r="K8" t="s">
-        <v>50</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>99</v>
+      <c r="L8" t="s">
+        <v>34</v>
       </c>
       <c r="O8" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="P8" t="s">
-        <v>36</v>
+      <c r="P8" s="3" t="s">
+        <v>101</v>
       </c>
       <c r="Q8" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R8" t="s">
         <v>102</v>
       </c>
-      <c r="S8">
+      <c r="S8" t="s">
+        <v>103</v>
+      </c>
+      <c r="T8">
         <v>12347</v>
       </c>
-      <c r="T8" t="s">
-        <v>39</v>
-      </c>
-      <c r="U8" s="2" t="s">
-        <v>103</v>
+      <c r="U8" t="s">
+        <v>42</v>
+      </c>
+      <c r="V8" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>82</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J9" s="1">
+        <v>51</v>
+      </c>
+      <c r="J9" t="s">
+        <v>33</v>
+      </c>
+      <c r="K9" s="1">
         <v>70097</v>
       </c>
-      <c r="K9" t="s">
-        <v>50</v>
-      </c>
-      <c r="N9" s="3" t="s">
-        <v>105</v>
+      <c r="L9" t="s">
+        <v>34</v>
       </c>
       <c r="O9" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="P9" t="s">
-        <v>36</v>
+        <v>107</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="Q9" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="R9" t="s">
-        <v>108</v>
-      </c>
-      <c r="S9">
+        <v>109</v>
+      </c>
+      <c r="S9" t="s">
+        <v>110</v>
+      </c>
+      <c r="T9">
         <v>12348</v>
       </c>
-      <c r="T9" t="s">
-        <v>39</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>109</v>
+      <c r="U9" t="s">
+        <v>42</v>
+      </c>
+      <c r="V9" s="2" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s">
-        <v>49</v>
-      </c>
-      <c r="J10" s="1">
+        <v>51</v>
+      </c>
+      <c r="J10" t="s">
+        <v>33</v>
+      </c>
+      <c r="K10" s="1">
         <v>70098</v>
       </c>
-      <c r="K10" t="s">
-        <v>50</v>
-      </c>
-      <c r="N10" s="3" t="s">
-        <v>112</v>
+      <c r="L10" t="s">
+        <v>34</v>
       </c>
       <c r="O10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="P10" t="s">
-        <v>36</v>
+        <v>114</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="Q10" t="s">
-        <v>114</v>
+        <v>39</v>
       </c>
       <c r="R10" t="s">
-        <v>115</v>
-      </c>
-      <c r="S10">
+        <v>116</v>
+      </c>
+      <c r="S10" t="s">
+        <v>117</v>
+      </c>
+      <c r="T10">
         <v>12349</v>
       </c>
-      <c r="T10" t="s">
-        <v>39</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>116</v>
+      <c r="U10" t="s">
+        <v>42</v>
+      </c>
+      <c r="V10" s="2" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J11" s="1">
+        <v>51</v>
+      </c>
+      <c r="J11" t="s">
+        <v>33</v>
+      </c>
+      <c r="K11" s="1">
         <v>70099</v>
       </c>
-      <c r="K11" t="s">
-        <v>50</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>119</v>
+      <c r="L11" t="s">
+        <v>34</v>
       </c>
       <c r="O11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="P11" t="s">
-        <v>36</v>
+        <v>121</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="Q11" t="s">
-        <v>121</v>
+        <v>39</v>
       </c>
       <c r="R11" t="s">
-        <v>122</v>
-      </c>
-      <c r="S11">
+        <v>123</v>
+      </c>
+      <c r="S11" t="s">
+        <v>124</v>
+      </c>
+      <c r="T11">
         <v>12350</v>
       </c>
-      <c r="T11" t="s">
-        <v>39</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>123</v>
+      <c r="U11" t="s">
+        <v>42</v>
+      </c>
+      <c r="V11" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>125</v>
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" t="s">
-        <v>49</v>
-      </c>
-      <c r="J12" s="1">
+        <v>51</v>
+      </c>
+      <c r="J12" t="s">
+        <v>33</v>
+      </c>
+      <c r="K12" s="1">
         <v>70100</v>
       </c>
-      <c r="K12" t="s">
-        <v>50</v>
-      </c>
-      <c r="N12" s="3" t="s">
-        <v>126</v>
+      <c r="L12" t="s">
+        <v>34</v>
       </c>
       <c r="O12" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="P12" t="s">
-        <v>36</v>
+        <v>128</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="Q12" t="s">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="R12" t="s">
-        <v>129</v>
-      </c>
-      <c r="S12">
+        <v>130</v>
+      </c>
+      <c r="S12" t="s">
+        <v>131</v>
+      </c>
+      <c r="T12">
         <v>12351</v>
       </c>
-      <c r="T12" t="s">
-        <v>39</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>130</v>
+      <c r="U12" t="s">
+        <v>42</v>
+      </c>
+      <c r="V12" s="2" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -1530,28 +1573,19 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="U2" r:id="rId1"/>
+    <hyperlink ref="V2" r:id="rId1"/>
     <hyperlink ref="C2" r:id="rId2"/>
-    <hyperlink ref="C3" r:id="rId3"/>
-    <hyperlink ref="U3" r:id="rId4"/>
-    <hyperlink ref="U4" r:id="rId5"/>
-    <hyperlink ref="U5" r:id="rId6"/>
-    <hyperlink ref="U6" r:id="rId7"/>
-    <hyperlink ref="U7" r:id="rId8"/>
-    <hyperlink ref="U8" r:id="rId9"/>
-    <hyperlink ref="U9" r:id="rId10"/>
-    <hyperlink ref="U10" r:id="rId11"/>
-    <hyperlink ref="U11" r:id="rId12"/>
-    <hyperlink ref="C10" r:id="rId13"/>
-    <hyperlink ref="C9" r:id="rId14"/>
-    <hyperlink ref="C8" r:id="rId15"/>
-    <hyperlink ref="C7" r:id="rId16"/>
-    <hyperlink ref="C6" r:id="rId17"/>
-    <hyperlink ref="C5" r:id="rId18"/>
-    <hyperlink ref="C4" r:id="rId19"/>
-    <hyperlink ref="C11" r:id="rId20"/>
-    <hyperlink ref="C12" r:id="rId21"/>
-    <hyperlink ref="U12" r:id="rId22"/>
+    <hyperlink ref="V3" r:id="rId3"/>
+    <hyperlink ref="V4" r:id="rId4"/>
+    <hyperlink ref="V5" r:id="rId5"/>
+    <hyperlink ref="V6" r:id="rId6"/>
+    <hyperlink ref="V7" r:id="rId7"/>
+    <hyperlink ref="V8" r:id="rId8"/>
+    <hyperlink ref="V9" r:id="rId9"/>
+    <hyperlink ref="V10" r:id="rId10"/>
+    <hyperlink ref="V11" r:id="rId11"/>
+    <hyperlink ref="V12" r:id="rId12"/>
+    <hyperlink ref="$C$3:$C$11" r:id="rId13"/>
   </hyperlinks>
 </worksheet>
 </file>
--- a/Book 6.xlsx
+++ b/Book 6.xlsx
@@ -98,7 +98,7 @@
     <t>User</t>
   </si>
   <si>
-    <t>abc700@gmail.com</t>
+    <t>abc805@gmail.com</t>
   </si>
   <si>
     <t>Mugs</t>
@@ -164,6 +164,9 @@
     <t>Userr</t>
   </si>
   <si>
+    <t>abc811@gmail.com</t>
+  </si>
+  <si>
     <t>Mug The adventure begins</t>
   </si>
   <si>
@@ -206,7 +209,7 @@
     <t>Useer</t>
   </si>
   <si>
-    <t>abc7001@gmail.com</t>
+    <t>abc852@gmail.com</t>
   </si>
   <si>
     <t>T-shirt</t>
@@ -239,7 +242,7 @@
     <t>Ankit</t>
   </si>
   <si>
-    <t>abc7002@gmail.com</t>
+    <t>abc883@gmail.com</t>
   </si>
   <si>
     <t>Frame</t>
@@ -269,7 +272,7 @@
     <t>Aman</t>
   </si>
   <si>
-    <t>abc70023@gmail.com</t>
+    <t>abc894@gmail.com</t>
   </si>
   <si>
     <t>Female</t>
@@ -296,7 +299,7 @@
     <t>Ayush</t>
   </si>
   <si>
-    <t>abc7004@gmail.com</t>
+    <t>abc808@gmail.com</t>
   </si>
   <si>
     <t>02/12/2005</t>
@@ -317,7 +320,7 @@
     <t>Sahil</t>
   </si>
   <si>
-    <t>abc7005@gmail.com</t>
+    <t>abc809@gmail.com</t>
   </si>
   <si>
     <t>02/12/2006</t>
@@ -338,7 +341,7 @@
     <t>Amar</t>
   </si>
   <si>
-    <t>abc7006@gmail.com</t>
+    <t>abc800@gmail.com</t>
   </si>
   <si>
     <t>02/12/2007</t>
@@ -359,7 +362,7 @@
     <t>Amit</t>
   </si>
   <si>
-    <t>abc7007@gmail.com</t>
+    <t>abc900@gmail.com</t>
   </si>
   <si>
     <t>02/12/2008</t>
@@ -380,7 +383,7 @@
     <t>Manpreet</t>
   </si>
   <si>
-    <t>abc7008@gmail.com</t>
+    <t>abc200@gmail.com</t>
   </si>
   <si>
     <t>02/12/2009</t>
@@ -401,7 +404,7 @@
     <t>Naman</t>
   </si>
   <si>
-    <t>abc7009@gmail.com</t>
+    <t>abc300@gmail.com</t>
   </si>
   <si>
     <t>02/12/2010</t>
@@ -465,8 +468,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -875,7 +878,7 @@
       <c r="B2" t="s">
         <v>25</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>26</v>
       </c>
       <c r="D2" t="s">
@@ -911,10 +914,10 @@
       <c r="N2" t="s">
         <v>36</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="O2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="P2" s="2" t="s">
         <v>38</v>
       </c>
       <c r="Q2" t="s">
@@ -932,7 +935,7 @@
       <c r="U2" t="s">
         <v>42</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="V2" s="3" t="s">
         <v>43</v>
       </c>
       <c r="W2" s="1" t="s">
@@ -949,8 +952,8 @@
       <c r="B3" t="s">
         <v>47</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>26</v>
+      <c r="C3" t="s">
+        <v>48</v>
       </c>
       <c r="D3" t="s">
         <v>27</v>
@@ -959,16 +962,16 @@
         <v>28</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J3" t="s">
         <v>33</v>
@@ -980,25 +983,25 @@
         <v>34</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N3" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="O3" s="2" t="s">
         <v>55</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>56</v>
       </c>
       <c r="Q3" t="s">
         <v>39</v>
       </c>
       <c r="R3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="S3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="T3">
         <v>12342</v>
@@ -1006,40 +1009,40 @@
       <c r="U3" t="s">
         <v>42</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>58</v>
+      <c r="V3" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
-      </c>
-      <c r="C4" s="2" t="s">
         <v>62</v>
       </c>
+      <c r="C4" t="s">
+        <v>63</v>
+      </c>
       <c r="D4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>28</v>
       </c>
       <c r="F4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J4" t="s">
         <v>33</v>
@@ -1050,20 +1053,20 @@
       <c r="L4" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="P4" s="3" t="s">
+      <c r="O4" s="2" t="s">
         <v>68</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>69</v>
       </c>
       <c r="Q4" t="s">
         <v>39</v>
       </c>
       <c r="R4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="S4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="T4">
         <v>12343</v>
@@ -1071,37 +1074,37 @@
       <c r="U4" t="s">
         <v>42</v>
       </c>
-      <c r="V4" s="2" t="s">
-        <v>71</v>
+      <c r="V4" s="3" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>73</v>
+      <c r="C5" t="s">
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E5" t="s">
         <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
         <v>33</v>
@@ -1112,20 +1115,20 @@
       <c r="L5" t="s">
         <v>34</v>
       </c>
-      <c r="O5" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="P5" s="3" t="s">
+      <c r="O5" s="2" t="s">
         <v>78</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="Q5" t="s">
         <v>39</v>
       </c>
       <c r="R5" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="S5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T5">
         <v>12344</v>
@@ -1133,37 +1136,37 @@
       <c r="U5" t="s">
         <v>42</v>
       </c>
-      <c r="V5" s="2" t="s">
-        <v>81</v>
+      <c r="V5" s="3" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>83</v>
+      <c r="C6" t="s">
+        <v>84</v>
       </c>
       <c r="D6" t="s">
         <v>27</v>
       </c>
       <c r="E6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
         <v>40</v>
       </c>
       <c r="I6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J6" t="s">
         <v>33</v>
@@ -1174,20 +1177,20 @@
       <c r="L6" t="s">
         <v>34</v>
       </c>
-      <c r="O6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="P6" s="3" t="s">
+      <c r="O6" s="2" t="s">
         <v>87</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>88</v>
       </c>
       <c r="Q6" t="s">
         <v>39</v>
       </c>
       <c r="R6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="S6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="T6">
         <v>12345</v>
@@ -1195,28 +1198,28 @@
       <c r="U6" t="s">
         <v>42</v>
       </c>
-      <c r="V6" s="2" t="s">
-        <v>90</v>
+      <c r="V6" s="3" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>92</v>
+      <c r="C7" t="s">
+        <v>93</v>
       </c>
       <c r="E7" t="s">
         <v>28</v>
       </c>
       <c r="H7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7" t="s">
         <v>33</v>
@@ -1227,20 +1230,20 @@
       <c r="L7" t="s">
         <v>34</v>
       </c>
-      <c r="O7" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="P7" s="3" t="s">
+      <c r="O7" s="2" t="s">
         <v>94</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>95</v>
       </c>
       <c r="Q7" t="s">
         <v>39</v>
       </c>
       <c r="R7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S7" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="T7">
         <v>12346</v>
@@ -1248,28 +1251,28 @@
       <c r="U7" t="s">
         <v>42</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>97</v>
+      <c r="V7" s="3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>99</v>
+      <c r="C8" t="s">
+        <v>100</v>
       </c>
       <c r="E8" t="s">
         <v>28</v>
       </c>
       <c r="H8" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J8" t="s">
         <v>33</v>
@@ -1280,20 +1283,20 @@
       <c r="L8" t="s">
         <v>34</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="P8" s="3" t="s">
+      <c r="O8" s="2" t="s">
         <v>101</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="Q8" t="s">
         <v>39</v>
       </c>
       <c r="R8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="S8" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="T8">
         <v>12347</v>
@@ -1301,28 +1304,28 @@
       <c r="U8" t="s">
         <v>42</v>
       </c>
-      <c r="V8" s="2" t="s">
-        <v>104</v>
+      <c r="V8" s="3" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>106</v>
+      <c r="C9" t="s">
+        <v>107</v>
       </c>
       <c r="E9" t="s">
         <v>28</v>
       </c>
       <c r="H9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J9" t="s">
         <v>33</v>
@@ -1333,20 +1336,20 @@
       <c r="L9" t="s">
         <v>34</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="P9" s="3" t="s">
+      <c r="O9" s="2" t="s">
         <v>108</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>109</v>
       </c>
       <c r="Q9" t="s">
         <v>39</v>
       </c>
       <c r="R9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="S9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="T9">
         <v>12348</v>
@@ -1354,28 +1357,28 @@
       <c r="U9" t="s">
         <v>42</v>
       </c>
-      <c r="V9" s="2" t="s">
-        <v>111</v>
+      <c r="V9" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>113</v>
+      <c r="C10" t="s">
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J10" t="s">
         <v>33</v>
@@ -1386,20 +1389,20 @@
       <c r="L10" t="s">
         <v>34</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="P10" s="3" t="s">
+      <c r="O10" s="2" t="s">
         <v>115</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>116</v>
       </c>
       <c r="Q10" t="s">
         <v>39</v>
       </c>
       <c r="R10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="S10" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="T10">
         <v>12349</v>
@@ -1407,28 +1410,28 @@
       <c r="U10" t="s">
         <v>42</v>
       </c>
-      <c r="V10" s="2" t="s">
-        <v>118</v>
+      <c r="V10" s="3" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>120</v>
+      <c r="C11" t="s">
+        <v>121</v>
       </c>
       <c r="E11" t="s">
         <v>28</v>
       </c>
       <c r="H11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J11" t="s">
         <v>33</v>
@@ -1439,20 +1442,20 @@
       <c r="L11" t="s">
         <v>34</v>
       </c>
-      <c r="O11" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="P11" s="3" t="s">
+      <c r="O11" s="2" t="s">
         <v>122</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>123</v>
       </c>
       <c r="Q11" t="s">
         <v>39</v>
       </c>
       <c r="R11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T11">
         <v>12350</v>
@@ -1460,28 +1463,28 @@
       <c r="U11" t="s">
         <v>42</v>
       </c>
-      <c r="V11" s="2" t="s">
-        <v>125</v>
+      <c r="V11" s="3" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
         <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
       </c>
       <c r="H12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="I12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J12" t="s">
         <v>33</v>
@@ -1492,20 +1495,20 @@
       <c r="L12" t="s">
         <v>34</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="P12" s="3" t="s">
+      <c r="O12" s="2" t="s">
         <v>129</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>130</v>
       </c>
       <c r="Q12" t="s">
         <v>39</v>
       </c>
       <c r="R12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T12">
         <v>12351</v>
@@ -1513,79 +1516,77 @@
       <c r="U12" t="s">
         <v>42</v>
       </c>
-      <c r="V12" s="2" t="s">
-        <v>132</v>
+      <c r="V12" s="3" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="2"/>
+      <c r="C13" s="3"/>
     </row>
     <row r="14">
-      <c r="C14" s="2"/>
+      <c r="C14" s="3"/>
     </row>
     <row r="15">
-      <c r="C15" s="2"/>
+      <c r="C15" s="3"/>
     </row>
     <row r="16">
-      <c r="C16" s="2"/>
+      <c r="C16" s="3"/>
     </row>
     <row r="17">
-      <c r="C17" s="2"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18">
-      <c r="C18" s="2"/>
+      <c r="C18" s="3"/>
     </row>
     <row r="19">
-      <c r="C19" s="2"/>
+      <c r="C19" s="3"/>
     </row>
     <row r="20">
-      <c r="C20" s="2"/>
+      <c r="C20" s="3"/>
     </row>
     <row r="21">
-      <c r="C21" s="2"/>
+      <c r="C21" s="3"/>
     </row>
     <row r="22">
-      <c r="C22" s="2"/>
+      <c r="C22" s="3"/>
     </row>
     <row r="23">
-      <c r="C23" s="2"/>
+      <c r="C23" s="3"/>
     </row>
     <row r="24">
-      <c r="C24" s="2"/>
+      <c r="C24" s="3"/>
     </row>
     <row r="25">
-      <c r="C25" s="2"/>
+      <c r="C25" s="3"/>
     </row>
     <row r="26">
-      <c r="C26" s="2"/>
+      <c r="C26" s="3"/>
     </row>
     <row r="27">
-      <c r="C27" s="2"/>
+      <c r="C27" s="3"/>
     </row>
     <row r="28">
-      <c r="C28" s="2"/>
+      <c r="C28" s="3"/>
     </row>
     <row r="29">
-      <c r="C29" s="2"/>
+      <c r="C29" s="3"/>
     </row>
     <row r="30">
-      <c r="C30" s="2"/>
+      <c r="C30" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="V2" r:id="rId1"/>
-    <hyperlink ref="C2" r:id="rId2"/>
-    <hyperlink ref="V3" r:id="rId3"/>
-    <hyperlink ref="V4" r:id="rId4"/>
-    <hyperlink ref="V5" r:id="rId5"/>
-    <hyperlink ref="V6" r:id="rId6"/>
-    <hyperlink ref="V7" r:id="rId7"/>
-    <hyperlink ref="V8" r:id="rId8"/>
-    <hyperlink ref="V9" r:id="rId9"/>
-    <hyperlink ref="V10" r:id="rId10"/>
-    <hyperlink ref="V11" r:id="rId11"/>
-    <hyperlink ref="V12" r:id="rId12"/>
-    <hyperlink ref="$C$3:$C$11" r:id="rId13"/>
+    <hyperlink ref="V3" r:id="rId2"/>
+    <hyperlink ref="V4" r:id="rId3"/>
+    <hyperlink ref="V5" r:id="rId4"/>
+    <hyperlink ref="V6" r:id="rId5"/>
+    <hyperlink ref="V7" r:id="rId6"/>
+    <hyperlink ref="V8" r:id="rId7"/>
+    <hyperlink ref="V9" r:id="rId8"/>
+    <hyperlink ref="V10" r:id="rId9"/>
+    <hyperlink ref="V11" r:id="rId10"/>
+    <hyperlink ref="V12" r:id="rId11"/>
   </hyperlinks>
 </worksheet>
 </file>